--- a/Zinc/6. Statistical data analysis/Toxicity plots/Probability_of_Zn_toxicity.xlsx
+++ b/Zinc/6. Statistical data analysis/Toxicity plots/Probability_of_Zn_toxicity.xlsx
@@ -388,7 +388,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0212264897453267</v>
+        <v>0.0205182338537994</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -399,7 +399,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>0.00115341081875179</v>
+        <v>0.00111656860670884</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -410,7 +410,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0252086001564876</v>
+        <v>0.0227308010742257</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/Zinc/6. Statistical data analysis/Toxicity plots/Probability_of_Zn_toxicity.xlsx
+++ b/Zinc/6. Statistical data analysis/Toxicity plots/Probability_of_Zn_toxicity.xlsx
@@ -1,46 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/6. Statistical data analysis/Toxicity plots/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_40C9943CD267E86CAFE29F3156CC5542A3FF9DAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E275987C-6A47-4ECB-AD20-33E89ED4AF95}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t xml:space="preserve">Typology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overlap_Zn_Chronic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overlap_Zn_Acute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NP Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem</t>
+    <t>Typology</t>
+  </si>
+  <si>
+    <t>Overlap_Zn_Chronic</t>
+  </si>
+  <si>
+    <t>Overlap_Zn_Acute</t>
+  </si>
+  <si>
+    <t>NP Tribs</t>
+  </si>
+  <si>
+    <t>P Tribs</t>
+  </si>
+  <si>
+    <t>PD Tribs</t>
+  </si>
+  <si>
+    <t>Main Stem</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -69,13 +81,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -357,11 +381,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -372,52 +400,52 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.148123341364914</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="3">
+        <v>0.14812334136491401</v>
+      </c>
+      <c r="C2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.0205182338537994</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" s="2">
+        <v>2.05182338537994E-2</v>
+      </c>
+      <c r="C3">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.00111656860670884</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" s="1">
+        <v>1.1165686067088399E-3</v>
+      </c>
+      <c r="C4">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.0227308010742257</v>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5" s="2">
+        <v>2.27308010742257E-2</v>
+      </c>
+      <c r="C5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Zinc/6. Statistical data analysis/Toxicity plots/Probability_of_Zn_toxicity.xlsx
+++ b/Zinc/6. Statistical data analysis/Toxicity plots/Probability_of_Zn_toxicity.xlsx
@@ -1,58 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/6. Statistical data analysis/Toxicity plots/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_40C9943CD267E86CAFE29F3156CC5542A3FF9DAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E275987C-6A47-4ECB-AD20-33E89ED4AF95}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>Typology</t>
-  </si>
-  <si>
-    <t>Overlap_Zn_Chronic</t>
-  </si>
-  <si>
-    <t>Overlap_Zn_Acute</t>
-  </si>
-  <si>
-    <t>NP Tribs</t>
-  </si>
-  <si>
-    <t>P Tribs</t>
-  </si>
-  <si>
-    <t>PD Tribs</t>
-  </si>
-  <si>
-    <t>Main Stem</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t xml:space="preserve">Typology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlap_Zn_Chronic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlap_Zn_Acute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pooled Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Perennial Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developed Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="167" formatCode="0.00000"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -81,25 +72,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -381,15 +360,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -400,52 +375,63 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3">
-        <v>0.14812334136491401</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B2" t="n">
+        <v>0.0271934581287768</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
-        <v>2.05182338537994E-2</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" t="n">
+        <v>0.148123341364914</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1">
-        <v>1.1165686067088399E-3</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" t="n">
+        <v>0.0205182338537994</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2">
-        <v>2.27308010742257E-2</v>
-      </c>
-      <c r="C5">
+      <c r="B5" t="n">
+        <v>0.00111656860670884</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0227308010742257</v>
+      </c>
+      <c r="C6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Zinc/6. Statistical data analysis/Toxicity plots/Probability_of_Zn_toxicity.xlsx
+++ b/Zinc/6. Statistical data analysis/Toxicity plots/Probability_of_Zn_toxicity.xlsx
@@ -23,16 +23,16 @@
     <t xml:space="preserve">Overlap_Zn_Acute</t>
   </si>
   <si>
-    <t xml:space="preserve">Pooled Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Tribs</t>
+    <t xml:space="preserve">Pooled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developed Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">Main Stem</t>
